--- a/data_extactor/batch_10_fa/batch_0020_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0020_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Drafters, All Other (نقشه‌کش‌ها، سایر موارد)</t>
+          <t>نقشه‌کش‌ها، سایر موارد (Drafters, All Other)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAD Drafter | CAD Operator | CAD Technician | Design Drafter | Detailer | Drafter | Drafting Technician | Layout Drafter | Piping Drafter | Structural Drafter</t>
+          <t>نقشه‌کش CAD | اپراتور CAD | تکنسین CAD | طراح نقشه‌کش | دیتیلر | نقشه‌کش | تکنسین نقشه‌کشی | نقشه‌کش چیدمان | نقشه‌کش خطوط لوله | نقشه‌کش سازه</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Autodesk Revit | Bentley MicroStation | Dassault Systemes SolidWorks | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی به کمک کامپیوتر سه‌بعدی 3D CAD | نرم‌افزار طراحی به کمک کامپیوتر دوبعدی 2D CAD | Microsoft Excel | Microsoft Word | Adobe Acrobat | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office</t>
+          <t>Autodesk AutoCAD | Autodesk Revit | Bentley MicroStation | Dassault Systemes SolidWorks | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD | نرم‌افزار طراحی دو بعدی به کمک کامپیوتر CAD | Microsoft Excel | Microsoft Word | Adobe Acrobat | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخنوری | ریاضیات | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | ریاضیات | کامپیوتر و الکترونیک | زبان انگلیسی | ساختمان و ساخت‌وساز | مکانیک | تولید و فرآوری</t>
+          <t>طراحی | مهندسی و فناوری | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | ساختمان و ساخت‌وساز | مکانیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | صرف زمان برای انجام حرکات تکراری | درجه اتوماسیون</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | میزان خودکارسازی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمرانی | نقشه‌کش‌های برق و الکترونیک | نقشه‌کش‌های مکانیک | تکنسین‌ها و کارشناسان مهندسی عمران | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارتوگراف‌ها و فتوگرامتریست‌ها | معماران، به جز منظر و دریایی | معماران منظر | نقشه‌برداران | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی هوافضا | مهندسان عمران | مهندسان مکانیک | طراحان داخلی | طراحان تجاری و صنعتی</t>
+          <t>نقشه‌کشان معماری و عمران | نقشه‌کشان برق و الکترونیک | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی عمران | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌برداران و فتوگرامتریست‌ها | معماران، به‌جز منظر و دریایی | معماران منظر | نقشه‌برداران | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان عمران | مهندسان مکانیک | طراحان داخلی | طراحان تجاری و صنعتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aerospace Engineering and Operations Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا (Aerospace Engineering and Operations Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avionics Installation Technician | Avionics Test Technician | Engineering Technician | Engineering Test Technician | Flight Test Instrument Technician | Instrumentation Technician | Systems Test Technician | Test Technician</t>
+          <t>تکنسین نصب آویونیک | تکنسین آزمون آویونیک | تکنسین مهندسی | تکنسین آزمون مهندسی | تکنسین ابزار دقیق آزمون پرواز | تکنسین ابزار دقیق | تکنسین آزمون سامانه‌ها | تکنسین تست</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخنوری | علوم | نظارت | نوشتن | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | علوم | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | اداری | فیزیک | کامپیوتر و الکترونیک | آموزش و پرورش</t>
+          <t>مکانیک | مهندسی و فناوری | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | اداری | فیزیک | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | استدلال استقرایی | نظم‌دهی اطلاعات | بیان نوشتاری | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای تهویه مطبوع | بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری | صرف زمان برای استفاده از دستان خود جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض شرایط خطرناک | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | سلامت و ایمنی سایر کارگران</t>
+          <t>اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض شرایط خطرناک | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح، ریگینگ و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی</t>
+          <t>مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Civil Engineering Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی عمران)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی عمران (Civil Engineering Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Civil Designer | Civil Engineering Assistant | Civil Engineering Technician | Design Technician | Engineer Technician | Engineering Assistant | Engineering Technician | Transportation Engineering Technician</t>
+          <t>طراح عمرانی | دستیار مهندسی عمران | تکنسین مهندسی عمران | تکنسین طراحی | تکنسین مهندسی | دستیار مهندسی | تکنسین مهندسی | تکنسین مهندسی حمل‌ونقل</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | ریاضیات | سخنوری | نوشتن | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | ریاضیات | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | ساختمان و ساخت‌وساز | طراحی | اداری | مدیریت و اداره | کامپیوتر و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | حمل‌ونقل | ایمنی و امنیت عمومی | فیزیک | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | ریاضیات | ساختمان و ساخت‌وساز | طراحی | اداری | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | حمل و نقل | ایمنی و امنیت عمومی | فیزیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال ریاضی | دید نزدیک | درک شنیداری | درک نوشتاری | حساسیت به مسئله | بیان شفاهی | بیان نوشتاری | تجسم | توانایی عددی | نظم‌دهی اطلاعات | دید دور | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | خلاقیت | روانی ایده‌ها | سرعت بستار</t>
+          <t>استدلال قیاسی | استدلال ریاضی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | تجسم | توانایی عددی | ترتیب‌دهی اطلاعات | بینایی دور | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | اصالت | روانی ایده‌ها | سرعت بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | محیط داخلی، دارای تهویه مطبوع | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | تناوب تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارگران | محیط بیرونی، قرار گرفتن در معرض تمام شرایط آب و هوایی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>معماران، به جز منظر و دریایی | نقشه‌کش‌های معماری و عمرانی | مدیران معماری و مهندسی | مهندسان عمران | مدیران ساخت‌وساز | بازرسان ساخت‌وساز و ساختمان | برآوردکنندگان هزینه | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی محیط زیست | سرپرستان مستقیم کارگران ساختمانی و استخراج | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان دریایی و معماران کشتی | نقشه‌کش‌های مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | متخصصان مدیریت پروژه | مهندسان حمل‌ونقل</t>
+          <t>معماران، به‌جز منظر و دریایی | نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | مهندسان عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | برآوردکنندگان هزینه | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی محیط زیست | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان دریایی و معماران کشتی | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | متخصصان مدیریت پروژه | مهندسان حمل و نقل</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electrical and Electronic Engineering Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک (Electrical and Electronic Engineering Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Communications Technologist | Electrical Engineering Technician | Electrical Technician | Electronics Engineering Technician | Electronics Technician | Engineering Technician (Engineering Tech) | Engineering Technologist | System Technologist | Technologist</t>
+          <t>تکنولوژیست ارتباطات | تکنسین مهندسی برق | تکنسین برق | تکنسین مهندسی الکترونیک | تکنسین الکترونیک | تکنسین مهندسی (Engineering Tech) | تکنولوژیست مهندسی | تکنولوژیست سامانه | تکنولوژیست</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVEVA InTouch HMI | Adobe Acrobat | Adobe ActionScript | Agilent Advanced Design System ADS | Altera MAX | Altera Quartus II | Altium Designer | Anadigm Designer2 EDA | Analog Devices VisualDSP++ | Ansoft HFSS | Ansys Fluent | Autodesk AutoCAD | Autodesk Revit | BSVC | Bentley MicroStation | Bentley Systems ProjectWise | C | C++ | CST Microwave Studio | Cadence OrCAD PSpice | Cadence PSpice | Canu | نرم‌افزار شبیه‌سازی مدار | ابزارهای مهندسی نرم‌افزار به کمک کامپیوتر CASE | نرم‌افزار مهندسی به کمک کامپیوتر CAE | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار پایگاه داده | نرم‌افزار عیب‌یابی | EMA TimingDesigner | Eclipse IDE | شبیه‌سازها | FileMaker Pro | FlukeView Forms | GE Fanuc Automation VersaPro | GNU Octave | Gnuplot | نرم‌افزار گرافیکی | HP InfoTech CodeVisionAVR | نرم‌افزار رابط انسان و ماشین HMI | IBM Cognos Impromptu | IBM WebSphere | JavaScript | Keysight Technologies Advanced Design System | KiCad | Linux | Logisim | MAGIC software | Magellan Firmware | MathWorks Simulink | Mentor Graphics PADS | محیط توسعه یکپارچه Microchip MPLAB (IDE) | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Windows | Microsoft Word | Motorola Digital Signal Processing (DSP) Assembler | National Instruments LabVIEW | National Instruments Multisim | OctTools | OrCAD Capture | Oracle Database | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | PTC Mathcad | PUFF | PowerWorld software | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | نرم‌افزار کنترل تناسبی انتگرالی مشتق‌گیر PID | Python | Rockwell RSLogix | Rockwell RSView | نرم‌افزار تحلیل ریشه علت | نرم‌افزار SAP | SPLAT! | Siemens ModelSim | سنتزکننده‌های سیگنال | نرم‌افزار شبیه‌سازی | Spectrum Software Micro-Cap | سیستم طراحی VLSI الکتریکی Static Free Software | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Tanner Research L-Edit | نرم‌افزار شبیه‌سازی ترمینال | Texas Instruments Code Composer Studio CCStudio | The MathWorks MATLAB | شبیه‌سازهای خط انتقال | UNIX | Vector Software VectorCast | Verilog | Wolfram Research Mathematica | Xcircuit | gEDA | ngspice | pMatlab</t>
+          <t>AVEVA InTouch HMI | Adobe Acrobat | Adobe ActionScript | Agilent Advanced Design System ADS | Altera MAX | Altera Quartus II | Altium Designer | Anadigm Designer2 EDA | Analog Devices VisualDSP++ | Ansoft HFSS | Ansys Fluent | Autodesk AutoCAD | Autodesk Revit | BSVC | Bentley MicroStation | Bentley Systems ProjectWise | C | C++ | CST Microwave Studio | Cadence OrCAD PSpice | Cadence PSpice | Canu | نرم‌افزار شبیه‌سازی مدار | ابزارهای مهندسی نرم‌افزار به کمک کامپیوتر CASE | نرم‌افزار مهندسی به کمک کامپیوتر CAE | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار پایگاه داده | نرم‌افزار عیب‌یابی | EMA TimingDesigner | Eclipse IDE | شبیه‌سازها | FileMaker Pro | FlukeView Forms | GE Fanuc Automation VersaPro | GNU Octave | Gnuplot | نرم‌افزار گرافیکی | HP InfoTech CodeVisionAVR | نرم‌افزار رابط انسان و ماشین HMI | IBM Cognos Impromptu | IBM WebSphere | JavaScript | Keysight Technologies Advanced Design System | KiCad | Linux | Logisim | نرم‌افزار MAGIC | Magellan Firmware | MathWorks Simulink | Mentor Graphics PADS | محیط توسعه یکپارچه Microchip MPLAB IDE | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Windows | Microsoft Word | Motorola Digital Signal Processing (DSP) Assembler | National Instruments LabVIEW | National Instruments Multisim | OctTools | OrCAD Capture | Oracle Database | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | PTC Mathcad | PUFF | PowerWorld software | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل تناسبی انتگرالی مشتق‌گیر PID | Python | Rockwell RSLogix | Rockwell RSView | نرم‌افزار تحلیل علت ریشه‌ای | نرم‌افزار SAP | SPLAT! | Siemens ModelSim | سنتزکننده‌های سیگنال | نرم‌افزار شبیه‌سازی | Spectrum Software Micro-Cap | سیستم طراحی VLSI الکتریکی نرم‌افزار Static Free | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Tanner Research L-Edit | نرم‌افزار شبیه‌سازی ترمینال | Texas Instruments Code Composer Studio CCStudio | The MathWorks MATLAB | شبیه‌سازهای خط انتقال | UNIX | Vector Software VectorCast | Verilog | Wolfram Research Mathematica | Xcircuit | gEDA | ngspice | pMatlab</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخنوری | نوشتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | ریاضیات | خدمات مشتری و شخصی | مکانیک | تولید و فرآوری | مخابرات | فیزیک</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | ریاضیات | خدمات مشتری و شخصی | مکانیک | تولید و فرآوری | مخابرات | فیزیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک نوشتاری | استدلال قیاسی | استدلال استقرایی | درک شنیداری | دید نزدیک | حساسیت به مسئله | بیان شفاهی | نظم‌دهی اطلاعات | بیان نوشتاری | وضوح گفتار | تجسم | سرعت ادراکی | تشخیص رنگ بصری | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | خلاقیت | روانی ایده‌ها</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | ترتیب‌دهی اطلاعات | بیان کتبی | وضوح گفتار | تجسم | سرعت ادراکی | تشخیص رنگ بصری | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای نشستن | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تناوب تصمیم‌گیری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای نشستن | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنسین‌ها و کارشناسان کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نقشه‌کش‌های برق و الکترونیک | نصب‌کنندگان و تعمیرکاران برق و الکترونیک، تجهیزات حمل‌ونقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تعمیرکاران برق و الکترونیک، نیروگاه، پست و رله | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Electro-Mechanical and Mechatronics Technologists and Technicians (تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک)</t>
+          <t>تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک (Electro-Mechanical and Mechatronics Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Automation Technician (Automation Tech) | Electro-Mechanic | Electromechanical Assembler (EM Assembler) | Electromechanical Technician (EM Technician) | Electronics Technician (Electronics Tech) | Mechanical Technician (Mechanical Tech) | Process Control Tech | Product Test Specialist | Test Engineering Technician (Test Engineering Tech) | Test Technician (Test Tech)</t>
+          <t>تکنسین اتوماسیون (Automation Tech) | تکنسین برق و مکانیک | مونتاژکار الکترومکانیکی (EM Assembler) | تکنسین الکترومکانیک (EM Technician) | تکنسین الکترونیک (Electronics Tech) | تکنسین مکانیک (Mechanical Tech) | تکنسین کنترل فرایند | کارشناس آزمون محصول | تکنسین مهندسی آزمون (Test Engineering Tech) | تکنسین آزمون (Test Tech)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Airdata | Autodesk AutoCAD | Autodesk Inventor | Automation Studio | C++ | نرم‌افزار شبیه‌سازی مدار | CloudCompare | سیستم مدیریت نگهداری کامپیوتری CMMS | Dassault Systemes SolidWorks | نرم‌افزار ESRI ArcGIS | نرم‌افزار رابط انسان و ماشین HMI | سیستم تصویربرداری لیزری و ردیابی LIDAR | Linux | Litchi | نرم‌افزار برنامه‌ریزی منابع تولید MRP | MathWorks Simulink | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | MindJet MindManager | نرم‌افزار کنترل حرکت | National Instruments LabVIEW | National Instruments Multisim | National Instruments Ultiboard | مدیریت چرخه عمر محصول Oracle Agile PLM | PTC Creo Parametric | Pix4D Pix4Dcapture | نرم‌افزار Pix4D | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | Python | نرم‌افزار نمونه‌سازی سریع | Rockwell RSLogix | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | The MathWorks MATLAB | UNIX | UgCS</t>
+          <t>Airdata | Autodesk AutoCAD | Autodesk Inventor | Automation Studio | C++ | نرم‌افزار شبیه‌سازی مدار | CloudCompare | سیستم مدیریت نگهداری کامپیوتری CMMS | Dassault Systemes SolidWorks | نرم‌افزار ESRI ArcGIS | نرم‌افزار رابط انسان و ماشین HMI | سیستم تصویربرداری لیزری و ردیابی LIDAR | Linux | Litchi | نرم‌افزار برنامه‌ریزی منابع تولید MRP | MathWorks Simulink | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | MindJet MindManager | نرم‌افزار کنترل حرکت | National Instruments LabVIEW | National Instruments Multisim | National Instruments Ultiboard | Oracle Agile Product Lifecycle Management PLM | PTC Creo Parametric | Pix4D Pix4Dcapture | نرم‌افزار Pix4D | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار نمونه‌سازی سریع | Rockwell RSLogix | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | The MathWorks MATLAB | UNIX | UgCS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | نوشتن | سخنوری | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مکانیک | مهندسی و فناوری | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
+          <t>رایانه و الکترونیک | مکانیک | مهندسی و فناوری | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | استدلال استقرایی | نظم‌دهی اطلاعات | ثبات دست و بازو | مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | دید دور | سرعت ادراکی | مهارت دستی | درک شنیداری | تشخیص رنگ بصری | بیان نوشتاری | درک نوشتاری | بیان شفاهی | سرعت بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | حساسیت شنوایی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | زمان واکنش | اشتراک زمانی | توانایی عددی | استدلال ریاضی | هماهنگی چند اندام | خلاقیت | روانی ایده‌ها</t>
+          <t>دقت کنترل | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | بینایی دور | سرعت ادراکی | مهارت دستی | درک شفاهی | تشخیص رنگ بصری | بیان کتبی | درک کتبی | بیان شفاهی | سرعت بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | حساسیت شنوایی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | زمان عکس‌العمل | تقسیم توجه | توانایی عددی | استدلال ریاضی | هماهنگی چند عضو | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای تهویه مطبوع | فشار زمانی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دستان خود جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | تناوب تصمیم‌گیری | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | سطح رقابت | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | اهمیت تکرار وظایف مشابه | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارگران</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | سطح رقابت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح، ریگینگ و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنسین‌ها و کارشناسان کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکاران برق و الکترونیک، تجهیزات حمل‌ونقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Robotics Technicians (تکنسین‌های رباتیک)</t>
+          <t>تکنسین‌های رباتیک (Robotics Technicians)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Automation Technician | Electrical and Instrumentation Technician (E and I Technician) | Instrument Specialist | Instrument Technician | Instrument and Automation Technician | Instrumentation and Controls Technician | Instrumentation and Process Controls Technician | Process Control Technician | Programmable Logic Controllers Technician</t>
+          <t>تکنسین اتوماسیون | تکنسین برق و ابزار دقیق | کارشناس ابزار دقیق | تکنسین ابزار دقیق | تکنسین ابزار دقیق و اتوماسیون | تکنسین ابزار دقیق و کنترل | تکنسین ابزار دقیق و کنترل فرایند | تکنسین کنترل فرایند | تکنسین کنترل‌گرهای منطقی برنامه‌پذیر</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ABB RobotStudio | AVEVA InTouch HMI | Ada | نرم‌افزار تحلیلی | Autodesk AutoCAD | Bentley MicroStation | C | C# | C++ | CODESYS | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | FANUC Robotics ArcTool | FANUC Robotics Diagnostic Resource Center DRC | FANUC Robotics Dual Check Safety DCS Position and Speed Check | FANUC Robotics HandlingTool | FANUC Robotics MultiARM Systems | FANUC Robotics SpotTool+ | FANUC Robotics Through Arc Seam Tracking TAST | FANUC Robotics Torchmate 3 | FANUC Robotics iRCalibration Vision Suite | FANUC Robotics iRVision | Git | نرم‌افزار رابط انسان و ماشین HMI | JavaScript | Keb Combivis Studio | منطق نردبانی | Linux | Logic Design RoboLogix | MathWorks Simulink | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Oracle Java | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | Python | نرم‌افزار SAP | Siemens SIMATIC STEP 7 | Siemens SIMATIC WinCC | نرم‌افزار شبیه‌سازی | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | The MathWorks MATLAB | UNIX | نرم‌افزار درایو فرکانس متغیر VFD | Windows Embedded Compact</t>
+          <t>ABB RobotStudio | AVEVA InTouch HMI | Ada | نرم‌افزار تحلیلی | Autodesk AutoCAD | Bentley MicroStation | C | C# | C++ | CODESYS | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | FANUC Robotics ArcTool | FANUC Robotics Diagnostic Resource Center DRC | FANUC Robotics Dual Check Safety DCS Position and Speed Check | FANUC Robotics HandlingTool | FANUC Robotics MultiARM Systems | FANUC Robotics SpotTool+ | FANUC Robotics Through Arc Seam Tracking TAST | FANUC Robotics Torchmate 3 | FANUC Robotics iRCalibration Vision Suite | FANUC Robotics iRVision | Git | نرم‌افزار رابط انسان و ماشین HMI | JavaScript | Keb Combivis Studio | Ladder Logic | Linux | Logic Design RoboLogix | MathWorks Simulink | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Oracle Java | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار SAP | Siemens SIMATIC STEP 7 | Siemens SIMATIC WinCC | نرم‌افزار شبیه‌سازی | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | The MathWorks MATLAB | UNIX | نرم‌افزار درایو فرکانس متغیر VFD | Windows Embedded Compact</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخنوری | نوشتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | تولید و فرآوری | فیزیک</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | تولید و فرآوری | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | دید نزدیک | درک شنیداری | درک نوشتاری | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | نظم‌دهی اطلاعات | مهارت انگشتان | تجسم | مهارت دستی | توجه انتخابی | دقت کنترل | وضوح گفتار | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری بستار | سرعت ادراکی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بیان نوشتاری | تشخیص گفتار | سرعت بستار | حافظه‌سپاری | استدلال ریاضی | دید دور | زمان واکنش | خلاقیت</t>
+          <t>استدلال قیاسی | بینایی نزدیک | درک شفاهی | درک کتبی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | تجسم | مهارت دستی | توجه انتخابی | دقت کنترل | وضوح گفتار | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری بستار | سرعت ادراکی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تشخیص گفتار | سرعت بستار | حفظ کردن | استدلال ریاضی | بینایی دور | زمان عکس‌العمل | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای تهویه مطبوع | پیامد خطا | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | صرف زمان برای استفاده از دستان خود جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | قرار گرفتن در معرض شرایط خطرناک | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض شرایط خطرناک | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنسین‌ها و کارشناسان کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکاران برق و الکترونیک، تجهیزات حمل‌ونقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌های روشنایی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | مهندسان رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌های نورپردازی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,22 +835,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Environmental Engineering Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی محیط زیست)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی محیط زیست (Environmental Engineering Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air Quality Instrument Specialist | Engineer Technician | Environmental Engineering Assistant | Environmental Engineering Technician | Environmental Field Technician | Environmental Technician | Haz Tech (Hazardous Technician)</t>
+          <t>کارشناس ابزار دقیق کیفیت هوا | تکنسین مهندسی | دستیار مهندسی محیط‌زیست | تکنسین مهندسی محیط‌زیست | تکنسین میدانی محیط‌زیست | تکنسین محیط‌زیست | تکنسین مواد خطرناک (Haz Tech)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار شبیه‌سازی ANSYS | Adobe PageMaker | نرم‌افزار مدل‌سازی پراکندگی هوا | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Bentley MicroStation | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار مدیریت انتشار مداوم | DHI Water and Environment MIKE SHE | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | نرم‌افزار ارزیابی ریسک اکولوژیکی | نرم‌افزار ایمیل | نرم‌افزار مستندسازی بهداشت و ایمنی محیط زیست | مترجم فرمول FORTRAN | نرم‌افزار تشخیص نشت انتشار فرار | GAEA Technologies WinSieve | نرم‌افزار مدل پراکندگی گاز | نرم‌افزار مستندسازی ژل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار مدیریت گازهای گلخانه‌ای | HEC-RAS | نرم‌افزار مدیریت مواد خطرناک HMS | نرم‌افزار برنامه شبیه‌سازی هیدرولوژیکی HSPF | Insightful S-PLUS | نرم‌افزار مدل‌سازی بهینه‌سازی LINDO Systems | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Maplesoft Maple | نرم‌افزار برگه داده ایمنی مواد MSDS | Mathsoft Mathcad | نرم‌افزار تصویربرداری میکروسکوپی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint Server | Microsoft Word | National Instruments LabVIEW | نرم‌افزار مدل‌سازی شبکه عصبی | PerkinElmer Turbochrom | نرم‌افزار فتوگرامتری | Python | نرم‌افزار مدیریت انطباق مقررات | RockWare MODFLOW | Rockwell Automation Arena | SAS | Scientific Software Group MIGRATE | نرم‌افزار شبیه‌سازی | مکان‌یابی و نقشه‌برداری همزمان SLAM | نرم‌افزار مدیریت اصلاح سایت | SofTech CADRA | نرم‌افزار نقشه‌برداری خاک | نرم‌افزار آماری | نرم‌افزار مدل‌سازی تصادفی | نرم‌افزار مدل‌سازی رواناب طوفان | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | نرم‌افزار شبیه‌سازی اقلیم داخلی حرارتی | Visual MODFLOW Pro | نرم‌افزار WAM | نرم‌افزار مدیریت پسماند | نرم‌افزار مدل‌سازی جریان آب | نرم‌افزار مدل‌سازی جریان باد | Wolfram Research Mathematica | XP Software XPSWMM</t>
+          <t>نرم‌افزار شبیه‌سازی ANSYS | Adobe PageMaker | نرم‌افزار مدل‌سازی انتشار هوا | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Bentley MicroStation | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار مدیریت انتشار مداوم | DHI Water and Environment MIKE SHE | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | نرم‌افزار ارزیابی ریسک اکولوژیکی | نرم‌افزار ایمیل | نرم‌افزار مستندسازی بهداشت و ایمنی محیط زیست | Formula translation/translator FORTRAN | نرم‌افزار تشخیص نشت انتشار فرار | GAEA Technologies WinSieve | نرم‌افزار مدل انتشار گاز | نرم‌افزار مستندسازی ژل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار مدیریت گازهای گلخانه‌ای | HEC-RAS | نرم‌افزار مدیریت مواد خطرناک HMS | نرم‌افزار برنامه شبیه‌سازی هیدرولوژیکی فرترن HSPF | Insightful S-PLUS | نرم‌افزار مدل‌سازی بهینه‌سازی سیستم‌های LINDO | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Maplesoft Maple | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Mathsoft Mathcad | نرم‌افزار ثبت تصویر میکروسکوپی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint Server | Microsoft Word | National Instruments LabVIEW | نرم‌افزار مدل‌سازی شبکه عصبی | PerkinElmer Turbochrom | نرم‌افزار فتوگرامتری | Python | نرم‌افزار مدیریت انطباق با مقررات | RockWare MODFLOW | Rockwell Automation Arena | SAS | Scientific Software Group MIGRATE | نرم‌افزار شبیه‌سازی | مکان‌یابی و نقشه‌برداری همزمان SLAM | نرم‌افزار مدیریت پاکسازی سایت | SofTech CADRA | نرم‌افزار نقشه‌برداری خاک | نرم‌افزار آماری | نرم‌افزار مدل‌سازی تصادفی | نرم‌افزار مدل‌سازی رواناب آب‌های سطحی | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | نرم‌افزار شبیه‌سازی اقلیم داخلی حرارتی | Visual MODFLOW Pro | نرم‌افزار WAM | نرم‌افزار مدیریت پسماند | نرم‌افزار مدل‌سازی جریان آب | نرم‌افزار مدل‌سازی جریان باد | Wolfram Research Mathematica | XP Software XPSWMM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | سخنوری | علوم | نوشتن | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | علوم | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک نوشتاری | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | نظم‌دهی اطلاعات | درک شنیداری | وضوح گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | بیان نوشتاری | تشخیص گفتار | توجه انتخابی | دید دور | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | استدلال ریاضی | خلاقیت | روانی ایده‌ها | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تشخیص گفتار | توجه انتخابی | بینایی دور | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | استدلال ریاضی | اصالت | روانی ایده‌ها | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | محیط بیرونی، قرار گرفتن در معرض تمام شرایط آب و هوایی | محیط داخلی، دارای تهویه مطبوع | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | متخصصان و مدیران سایت بازسازی زمین‌های قهوه‌ای | مهندسان شیمی | تکنسین‌ها و کارشناسان مهندسی عمران | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژیکی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژیکی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | اپراتورهای تصفیه‌خانه آب و فاضلاب | مهندسان آب/فاضلاب</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مهندسان شیمی | تکنسین‌ها و کارشناسان مهندسی عمران | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Industrial Engineering Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی صنایع)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی صنایع (Industrial Engineering Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Business Process Analyst | Engineering Technician | Industrial Engineering Analyst | Industrial Engineering Technician | Manufacturing Coordinator | Manufacturing Technology Analyst | Quality Control Engineering Technician (QC Engineering Technician) | Quality Management Coordinator | Quality Technician | Service Technician</t>
+          <t>تحلیل‌گر فرآیند کسب‌وکار | تکنسین مهندسی | تحلیل‌گر مهندسی صنایع | تکنسین مهندسی صنایع | هماهنگ‌کننده تولید | تحلیل‌گر فناوری ساخت و تولید | تکنسین مهندسی کنترل کیفیت (QC Engineering Technician) | هماهنگ‌کننده مدیریت کیفیت | تکنسین کیفیت | تکنسین خدمات</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ABB CPM4Metals | AVEVA InTouch HMI | مدیریت ابعادی پیشرفته 3D-GD&amp;T | نرم‌افزار هوش مصنوعی | AspenTech Aspen InfoPlus | Autodesk Algor Simulation | Autodesk AutoCAD | Autodesk Inventor | کد دستورالعمل نمادین همه‌منظوره مبتدی BASIC | Bentley MicroStation | Blink | C | C++ | CNC Mastercam | Cadence PSpice | نرم‌افزار طراحی و ساخت به کمک کامپیوتر Cimatron | نرم‌افزار کنترل عددی کامپیوتری CNC | نرم‌افزار ماشین کنترل عددی کامپیوتری CNC | نرم‌افزار کنترل عددی کامپیوتری CNC | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delcam PowerMILL | نرم‌افزار طراحی و ساخت به کمک کامپیوتر Delcam | نرم‌افزار EPLAN | Eko | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار CNC Fanuc | G-code | نرم‌افزار ابعاد و تلورانس هندسی | GibbsCAM | نرم‌افزار ویرایش گرافیکی | نرم‌افزار گرافیکی | Horizon Software MRP Plus | نرم‌افزار رابط انسان و ماشین HMI | IBM CATIA | IBM Notes | IBM SPSS Statistics | IMSI TurboCAD | Infinity QS ProFicient | Infor Industrial Essentials | Inlet Technologies Semaphore | Kinematic Engineering MicroMeasure IV | Kubotek CADKEY Wireframe | Loom | MASS Group FactoryLink SCADA HMI | MSC Software Adams | MSC Software Nastran | MSC Software Patran | سیستم‌های اطلاعات مدیریت MIS | سیستم اجرای تولید MES | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Materilise Magics | MathWorks Simulink | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | National Instruments LabVIEW | National Instruments Multisim | National Instruments NI-DAQmx | Oracle JD Edwards EnterpriseOne | PLC Automation Intellution iFIX | PTC Creo Parametric | Planit Alphacam | سیستم مدیریت طراحی کارخانه PDMS | نرم‌افزار نگهداری کارخانه | ProModel | نرم‌افزار برنامه‌ریزی تولید | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | نرم‌افزار نمونه‌سازی سریع | Rockwell Automation Arena | نرم‌افزار SAP | Siemens NX | Siemens SIMATIC HMI | Siemens SINUMERIK CNC | Siemens Solid Edge | Stat-Ease Design-Expert | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار آماری | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | نرم‌افزار طراحی به کمک کامپیوتر Tebis | The MathWorks MATLAB | نرم‌افزار مدل‌سازی سه‌بعدی | نرم‌افزار طراحی پارامتریک سه‌بعدی | UNIX | VIA Information Tools MAN-IT | Vectorworks Machine Design | Vero Software SURFCAM | نرم‌افزار مرورگر وب | Wilcox Associates PC-DMIS</t>
+          <t>ABB CPM4Metals | AVEVA InTouch HMI | مدیریت ابعادی پیشرفته 3D-GD&amp;T | نرم‌افزار هوش مصنوعی | AspenTech Aspen InfoPlus | Autodesk Algor Simulation | Autodesk AutoCAD | Autodesk Inventor | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bentley MicroStation | Blink | C | C++ | CNC Mastercam | Cadence PSpice | نرم‌افزار طراحی و ساخت به کمک کامپیوتر Cimatron | نرم‌افزار کنترل عددی کامپیوتری CNC | نرم‌افزار ماشین کنترل عددی کامپیوتری CNC | نرم‌افزار کنترل عددی کامپیوتری CNC | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delcam PowerMILL | نرم‌افزار طراحی و ساخت به کمک کامپیوتر Delcam | نرم‌افزار EPLAN | Eko | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار CNC Fanuc | G-code | نرم‌افزار ابعاد و تلورانس هندسی | GibbsCAM | نرم‌افزار ویرایش گرافیکی | نرم‌افزار گرافیکی | Horizon Software MRP Plus | نرم‌افزار رابط انسان و ماشین HMI | IBM CATIA | IBM Notes | IBM SPSS Statistics | IMSI TurboCAD | Infinity QS ProFicient | Infor Industrial Essentials | Inlet Technologies Semaphore | Kinematic Engineering MicroMeasure IV | Kubotek CADKEY Wireframe | Loom | MASS Group FactoryLink SCADA HMI | MSC Software Adams | MSC Software Nastran | MSC Software Patran | سیستم‌های اطلاعات مدیریت MIS | سیستم اجرای تولید MES | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Materilise Magics | MathWorks Simulink | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | National Instruments LabVIEW | National Instruments Multisim | National Instruments NI-DAQmx | Oracle JD Edwards EnterpriseOne | PLC Automation Intellution iFIX | PTC Creo Parametric | Planit Alphacam | سیستم مدیریت طراحی کارخانه PDMS | نرم‌افزار نگهداری کارخانه | ProModel | نرم‌افزار برنامه‌ریزی تولید | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار نمونه‌سازی سریع | Rockwell Automation Arena | نرم‌افزار SAP | Siemens NX | Siemens SIMATIC HMI | Siemens SINUMERIK CNC | Siemens Solid Edge | Stat-Ease Design-Expert | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار آماری | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار طراحی به کمک کامپیوتر Tebis | The MathWorks MATLAB | نرم‌افزار مدل‌سازی سه‌بعدی | نرم‌افزار طراحی پارامتریک سه‌بعدی | UNIX | VIA Information Tools MAN-IT | Vectorworks Machine Design | Vero Software SURFCAM | نرم‌افزار مرورگر وب | Wilcox Associates PC-DMIS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخنوری | نوشتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | ریاضیات | طراحی | زبان انگلیسی | کامپیوتر و الکترونیک | فیزیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
+          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | ریاضیات | طراحی | زبان انگلیسی | رایانه و الکترونیک | فیزیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شنیداری | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک نوشتاری | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | بیان نوشتاری | روانی ایده‌ها | خلاقیت | تجسم | توجه انتخابی | تشخیص گفتار | وضوح گفتار | سرعت ادراکی | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری بستار | دید دور</t>
+          <t>استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | روانی ایده‌ها | اصالت | تجسم | توجه انتخابی | تشخیص گفتار | وضوح گفتار | سرعت ادراکی | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | محیط داخلی، دارای تهویه مطبوع | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف مشابه | نتایج کاری و خروجی‌های سایر کارگران</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان کالیبراسیون | مهندسان شیمی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید | مهندسان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | مونتاژکاران تیمی | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید | مهندسان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | مونتاژکاران تیمی | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nanotechnology Engineering Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی (Nanotechnology Engineering Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Engineering Technician (Engineering Tech) | Lab Technician (Laboratory Technician) | Nanofabrication Specialist | Process Engineering Technician (Process Engineering Tech) | R and D Engineer (Research and Development Engineer) | Research Lab Associate (Research Laboratory Associate) | Research Scientist | Research Specialist | Research Technician (Research Tech) | Scientific Research Associate</t>
+          <t>تکنسین مهندسی (Engineering Tech) | تکنسین آزمایشگاه | کارشناس ساخت در مقیاس نانو | تکنسین مهندسی فرایند (Process Engineering Tech) | مهندس تحقیق و توسعه (R and D) | کارشناس آزمایشگاه پژوهشی (Research Lab Associate) | دانشمند پژوهشی | متخصص پژوهشی | تکنسین پژوهش (Research Tech) | کارشناس پژوهش علمی</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نوشتن | علوم | گوش دادن فعال | یادگیری فعال | نظارت | سخنوری | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | علوم | گوش دادن فعال | یادگیری فعال | نظارت | سخن گفتن | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | زبان انگلیسی | شیمی | کامپیوتر و الکترونیک | ریاضیات | آموزش و پرورش | فیزیک | تولید و فرآوری | طراحی | مکانیک | خدمات مشتری و شخصی</t>
+          <t>مهندسی و فناوری | زبان انگلیسی | شیمی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش | فیزیک | تولید و فرآوری | طراحی | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | وضوح گفتار | ثبات دست و بازو | سرعت ادراکی | تشخیص گفتار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | مهارت انگشتان | دقت کنترل | تجسم | خلاقیت | دید دور | تشخیص رنگ بصری</t>
+          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | وضوح گفتار | ثبات دست و بازو | سرعت ادراکی | تشخیص گفتار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | مهارت انگشتان | دقت کنترل | تجسم | اصالت | بینایی دور | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای تهویه مطبوع | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | صرف زمان برای نشستن | مجاورت فیزیکی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | صرف زمان برای نشستن | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان زیستی و مهندسان زیست‌پزشکی | مدیران فناوری سوخت‌های زیستی/بیودیزل و توسعه محصول | تکنسین‌ها و کارشناسان کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمیدانان | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌ها و کارشناسان آزمایشگاه پزشکی و بالینی | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان زیستی و مهندسان زیست‌پزشکی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Technologists and Technicians (تکنسین‌ها و کارشناسان مهندسی مکانیک)</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی مکانیک (Mechanical Engineering Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Engineering Laboratory Technician (Engineering Lab Technician) | Engineering Technical Analyst | Engineering Technician (Engineering Tech) | Engineering Technologist | Manufacturing Engineering Technician (Manufacturing Engineering Tech) | Mechanical Designer | Mechanical Technician (Mechanical Tech) | Process Engineering Technician (Process Engineering Tech) | Process Technician | Research and Development Technician (R and D Tech)</t>
+          <t>تکنسین آزمایشگاه مهندسی (Engineering Lab Technician) | تحلیل‌گر فنی مهندسی | تکنسین مهندسی (Engineering Tech) | تکنولوژیست مهندسی | تکنسین مهندسی ساخت و تولید (Manufacturing Engineering Tech) | طراح مکانیک | تکنسین مکانیک (Mechanical Tech) | تکنسین مهندسی فرایند (Process Engineering Tech) | تکنسین فرآیند | تکنسین تحقیق و توسعه (R and D Tech)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ANSYS Mechanical | نرم‌افزار شبیه‌سازی ANSYS | Ansys Fluent | Autodesk AutoCAD | Autodesk AutoCAD Mechanical | Autodesk Inventor | Autodesk Revit | Bentley MicroStation | C++ | CNC Mastercam | نرم‌افزار برنامه‌نویسی کنترل عددی کامپیوتری CNC | مجموعه نرم‌افزاری Corel WordPerfect Office | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار روش المان محدود FEM | IBM CATIA | Intellisense Intellisuite | MSC Software Adams | Mathsoft Mathcad | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Word | National Instruments LabVIEW | PTC Creo Parametric | PTC Pro/ENGINEER Mechanica | ProModel | نرم‌افزار کنترل رباتیک | نرم‌افزار SAP | نرم‌افزار PLC Soft Servo Systems LadderWorks | Spectral Dynamics Star Acoustics | Spectral Dynamics Star Modal | سیستم‌های نمونه‌سازی سریع استریولیتوگرافی SLA | TekSoft CAMWorks | The MathWorks MATLAB | نرم‌افزار مدل‌سازی جامد سه‌بعدی 3D | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
+          <t>ANSYS Mechanical | نرم‌افزار شبیه‌سازی ANSYS | Ansys Fluent | Autodesk AutoCAD | Autodesk AutoCAD Mechanical | Autodesk Inventor | Autodesk Revit | Bentley MicroStation | C++ | CNC Mastercam | نرم‌افزار برنامه‌نویسی کنترل عددی کامپیوتری CNC | Corel WordPerfect Office Suite | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار روش المان محدود FEM | IBM CATIA | Intellisense Intellisuite | MSC Software Adams | Mathsoft Mathcad | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Word | National Instruments LabVIEW | PTC Creo Parametric | PTC Pro/ENGINEER Mechanica | ProModel | نرم‌افزار کنترل رباتیک | نرم‌افزار SAP | نرم‌افزار PLC Soft Servo Systems LadderWorks | Spectral Dynamics Star Acoustics | Spectral Dynamics Star Modal | سیستم‌های نمونه‌سازی سریع استریولیتوگرافی SLA | TekSoft CAMWorks | The MathWorks MATLAB | نرم‌افزار مدل‌سازی جامد سه‌بعدی 3D | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | نوشتن | ریاضیات | یادگیری فعال | نظارت | علوم</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | ریاضیات | یادگیری فعال | نظارت | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | کامپیوتر و الکترونیک | تولید و فرآوری | فیزیک | اداری</t>
+          <t>مهندسی و فناوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | تولید و فرآوری | فیزیک | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | توجه انتخابی | تجسم | استدلال ریاضی | بیان نوشتاری | انعطاف‌پذیری بستار | وضوح گفتار | سرعت ادراکی | خلاقیت | روانی ایده‌ها | دید دور | دقت کنترل | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | تشخیص رنگ بصری</t>
+          <t>درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | توجه انتخابی | تجسم | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری بستار | وضوح گفتار | سرعت ادراکی | اصالت | روانی ایده‌ها | بینایی دور | دقت کنترل | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | محیط داخلی، دارای تهویه مطبوع | اهمیت دقیق یا صحیح بودن | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارگران | مجاورت فیزیکی | سلامت و ایمنی سایر کارگران | تناوب تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | نقشه‌کش‌های مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | نقشه‌کشان مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0020_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0020_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | پایداری دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی چندعضوی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال ریاضی | دید دور | سرعت ادراک | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | نقشه‌کشان برق و الکترونیک | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی عمران | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | نقشه‌نگاران و فتوگرامتریست‌ها | معماران، به‌جز معماری منظر و دریایی | معماران منظر | نقشه‌برداران | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی محیط زیست | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارشناسان و تکنسین‌های کالیبراسیون | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان عمران | مهندسان مکانیک | طراحان دکوراسیون داخلی | طراحان تجاری و صنعتی</t>
+          <t>نقشه‌کشان معماری و عمران | نقشه‌کشان برق و الکترونیک | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی عمران | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان نقشه‌نگاری و فتوگرامتری | مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مهندسان معمار منظر | مهندسان نقشه‌برداری | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی محیط زیست | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان عمران | مهندسان مکانیک | طراحان داخلی | طراحان تجاری و صنعتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | علوم تجربی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | علوم | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | ریاضیات | تولید و فرآوری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | فیزیک | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>مکانیک | مهندسی و فناوری | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | اداری | فیزیک | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان کتبی | انعطاف‌پذیری بستار | سرعت ادراک | تجسم فضایی | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | سهولت در کار با اعداد | استدلال ریاضی | چابکی انگشتان | چابکی دستی | پایداری دست و بازو | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | کارشناسان و تکنسین‌های کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز رایانه | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | مهندسان صحه‌گذاری و اعتبارسنجی</t>
+          <t>مهندسان هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک و اپتیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | ریاضیات | سخن گفتن | نگارش | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | ریاضیات | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | ساختمان و ساخت‌وساز | طراحی | امور اداری | مدیریت و امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | حمل و نقل | ایمنی و امنیت عمومی | فیزیک | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | ریاضیات | ساختمان و ساخت‌وساز | طراحی | اداری | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | حمل و نقل | ایمنی و امنیت عمومی | فیزیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال ریاضی | دید نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | تجسم فضایی | سهولت در کار با اعداد | مرتب‌سازی اطلاعات | دید دور | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | سرعت بستار</t>
+          <t>استدلال قیاسی | استدلال ریاضی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | تجسم | توانایی عددی | ترتیب‌دهی اطلاعات | بینایی دور | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | اصالت | روانی ایده‌ها | سرعت بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماری منظر و دریایی | نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | مهندسان عمران | مدیران پروژه ساختمانی | بازرسان ساختمان و سازه | برآوردکنندگان هزینه و مترورها | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی محیط زیست | سرپرستان کارگاه‌های ساختمانی و عمرانی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان دریایی و معماران کشتی | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان مدیریت پروژه | مهندسان حمل و نقل</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | مدیران فنی و مهندسی و معماری | مهندسان عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی محیط زیست | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان دریایی و معماران کشتی | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان مدیریت پروژه | مهندسان حمل‌ونقل و ترافیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | ریاضیات | خدمات مشتریان و خدمات فردی | مکانیک | تولید و فرآوری | مخابرات | فیزیک</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | ریاضیات | خدمات مشتری و شخصی | مکانیک | تولید و فرآوری | مخابرات | فیزیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | دید نزدیک | حساسیت به مسئله | بیان شفاهی | مرتب‌سازی اطلاعات | بیان کتبی | وضوح گفتار | تجسم فضایی | سرعت ادراک | تشخیص رنگ‌ها | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | ترتیب‌دهی اطلاعات | بیان کتبی | وضوح گفتار | تجسم | سرعت ادراکی | تشخیص رنگ بصری | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | کارشناسان و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | نصاب‌ها و تعمیرکاران سامانه‌های برقی و الکترونیکی تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات برقی نیروگاه‌ها، پست‌ها و رله‌ها | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز رایانه | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک و اپتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات | پایداری دست و بازو | چابکی انگشتان | حساسیت به مسئله | استدلال قیاسی | دید دور | سرعت ادراک | چابکی دستی | درک شفاهی | تشخیص رنگ‌ها | بیان کتبی | درک کتبی | بیان شفاهی | سرعت بستار | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | حساسیت شنوایی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | زمان واکنش | تقسیم توجه | سهولت در کار با اعداد | استدلال ریاضی | هماهنگی چندعضوی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها</t>
+          <t>دقت کنترل | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | بینایی دور | سرعت ادراکی | مهارت دستی | درک شفاهی | تشخیص رنگ بصری | بیان کتبی | درک کتبی | بیان شفاهی | سرعت بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | حساسیت شنوایی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | زمان عکس‌العمل | تقسیم توجه | توانایی عددی | استدلال ریاضی | هماهنگی چند عضو | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | کارشناسان و تکنسین‌های کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران سامانه‌های برقی و الکترونیکی تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز رایانه | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک و اپتیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | دید نزدیک | درک شفاهی | درک کتبی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی انگشتان | تجسم فضایی | چابکی دستی | توجه انتخابی | دقت کنترل | وضوح گفتار | پایداری دست و بازو | تشخیص رنگ‌ها | انعطاف‌پذیری بستار | سرعت ادراک | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | تشخیص گفتار | سرعت بستار | حفظ و به‌خاطرسپاری | استدلال ریاضی | دید دور | زمان واکنش | ابتکار و اصالت</t>
+          <t>استدلال قیاسی | بینایی نزدیک | درک شفاهی | درک کتبی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | تجسم | مهارت دستی | توجه انتخابی | دقت کنترل | وضوح گفتار | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری بستار | سرعت ادراکی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تشخیص گفتار | سرعت بستار | حفظ کردن | استدلال ریاضی | بینایی دور | زمان عکس‌العمل | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | کارشناسان و تکنسین‌های کالیبراسیون | اپراتورهای ماشین‌های ابزار CNC | برنامه‌نویسان ماشین‌های CNC | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران سامانه‌های برقی و الکترونیکی تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز رایانه | کارشناسان و تکنسین‌های مهندسی صنایع | تکنسین‌های نور | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک | مهندسان رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | تکنسین‌های نورپردازی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های فوتونیک و اپتیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | علوم تجربی | نگارش | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | علوم | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | مکانیک | فیزیک | ایمنی و امنیت عمومی</t>
+          <t>مهندسی و فناوری | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | مکانیک | فیزیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | وضوح گفتار | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | تشخیص گفتار | توجه انتخابی | دید دور | دقت کنترل | چابکی انگشتان | پایداری دست و بازو | استدلال ریاضی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | سهولت در کار با اعداد | سرعت ادراک | انعطاف‌پذیری بستار</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تشخیص گفتار | توجه انتخابی | بینایی دور | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | استدلال ریاضی | اصالت | روانی ایده‌ها | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه‌های زیست‌توده | کارشناسان و مدیران احیای اراضی آلوده و سایت‌های صنعتی | مهندسان شیمی | کارشناسان و تکنسین‌های مهندسی عمران | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | تکنسین‌های حفاظت محیط زیست و بهداشت محیط | دانشمندان و متخصصان محیط زیست و بهداشت محیط | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های هیدرولوژی | مهندسان ایمنی و بهداشت حرفه‌ای، به‌جز بازرسان معدن | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | اپراتورهای تصفیه‌خانه‌ها و تأسیسات آب و فاضلاب | مهندسان آب و فاضلاب</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مهندسان شیمی | کارشناسان و تکنسین‌های مهندسی عمران | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | ریاضیات | طراحی | زبان انگلیسی | رایانه و الکترونیک | فیزیک | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | ریاضیات | طراحی | زبان انگلیسی | رایانه و الکترونیک | فیزیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | بیان شفاهی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | بیان کتبی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | تجسم فضایی | توجه انتخابی | تشخیص گفتار | وضوح گفتار | سرعت ادراک | سهولت در کار با اعداد | استدلال ریاضی | انعطاف‌پذیری بستار | دید دور</t>
+          <t>استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | روانی ایده‌ها | اصالت | تجسم | توجه انتخابی | تشخیص گفتار | وضوح گفتار | سرعت ادراکی | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | کارشناسان و تکنسین‌های کالیبراسیون | مهندسان شیمی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز رایانه | مهندسان صنایع | مدیران تولید صنعتی | مهندسان ساخت و تولید | مهندسان مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | کارگران مونتاژکار تیمی | مهندسان صحه‌گذاری و اعتبارسنجی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | مونتاژکاران گروهی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | علوم تجربی | شنیدن فعال | یادگیری فعال | نظارت | سخن گفتن | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | علوم | گوش دادن فعال | یادگیری فعال | نظارت | سخن گفتن | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | زبان انگلیسی | شیمی | رایانه و الکترونیک | ریاضیات | آموزش و تدریس | فیزیک | تولید و فرآوری | طراحی | مکانیک | خدمات مشتریان و خدمات فردی</t>
+          <t>مهندسی و فناوری | زبان انگلیسی | شیمی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش | فیزیک | تولید و فرآوری | طراحی | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | وضوح گفتار | پایداری دست و بازو | سرعت ادراک | تشخیص گفتار | سهولت در کار با اعداد | استدلال ریاضی | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری بستار | چابکی انگشتان | دقت کنترل | تجسم فضایی | ابتکار و اصالت | دید دور | تشخیص رنگ‌ها</t>
+          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | وضوح گفتار | ثبات دست و بازو | سرعت ادراکی | تشخیص گفتار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | مهارت انگشتان | دقت کنترل | تجسم | اصالت | بینایی دور | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان زیستی و مهندسان پزشکی | مدیران توسعه فناوری و محصولات سوخت‌های زیستی | کارشناسان و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمیدانان | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | دانشمندان علم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | کارشناسان و تکنسین‌های آزمایشگاه پزشکی و بالینی | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان پزشکی و بیوانجینیرینگ | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | کارشناسان علوم آزمایشگاهی بالینی | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | تکنسین‌های فوتونیک و اپتیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | ریاضیات | یادگیری فعال | نظارت | علوم تجربی</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | ریاضیات | یادگیری فعال | نظارت | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | تولید و فرآوری | فیزیک | امور اداری</t>
+          <t>مهندسی و فناوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | تولید و فرآوری | فیزیک | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | سهولت در کار با اعداد | توجه انتخابی | تجسم فضایی | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری بستار | وضوح گفتار | سرعت ادراک | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | دید دور | دقت کنترل | پایداری دست و بازو | چابکی انگشتان | چابکی دستی | تشخیص رنگ‌ها</t>
+          <t>درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | توجه انتخابی | تجسم | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری بستار | وضوح گفتار | سرعت ادراکی | اصالت | روانی ایده‌ها | بینایی دور | دقت کنترل | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | کارشناسان و تکنسین‌های کالیبراسیون | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان الکترونیک، به‌جز رایانه | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | نقشه‌کشان مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | نقشه‌کشان مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک و اپتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
